--- a/Excel Files IPEDS/Trimmed/c2008_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2008_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q362"/>
+  <dimension ref="A1:T362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,30 +486,45 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>CRACE19</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>CBKAAT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>CASIAT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>CNHPIT</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CHISPT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>CWHITT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>C2MORT</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>CNRALT</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -549,12 +564,19 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -592,12 +614,19 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -635,12 +664,19 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -678,12 +714,19 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -721,12 +764,19 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -780,6 +830,15 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -833,6 +892,15 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -870,12 +938,19 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -913,12 +988,19 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -956,12 +1038,19 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -999,12 +1088,19 @@
       <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1034,9 +1130,7 @@
       <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1047,9 +1141,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1087,12 +1190,19 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1130,12 +1240,19 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1173,12 +1290,19 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1216,12 +1340,19 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1259,12 +1390,19 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1302,12 +1440,19 @@
       <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1345,12 +1490,19 @@
       <c r="K20" t="n">
         <v>3</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1388,12 +1540,19 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1431,12 +1590,19 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1474,12 +1640,19 @@
       <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1517,12 +1690,19 @@
       <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1560,12 +1740,19 @@
       <c r="K25" t="n">
         <v>3</v>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="n">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1603,12 +1790,19 @@
       <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1646,12 +1840,19 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1689,12 +1890,19 @@
       <c r="K28" t="n">
         <v>5</v>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>4</v>
+      </c>
+      <c r="T28" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1732,12 +1940,19 @@
       <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>6</v>
+      </c>
+      <c r="T29" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1775,12 +1990,19 @@
       <c r="K30" t="n">
         <v>2</v>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1818,12 +2040,19 @@
       <c r="K31" t="n">
         <v>3</v>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1861,12 +2090,19 @@
       <c r="K32" t="n">
         <v>2</v>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1904,12 +2140,19 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1947,12 +2190,19 @@
       <c r="K34" t="n">
         <v>3</v>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="n">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -1990,12 +2240,19 @@
       <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="n">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2033,12 +2290,19 @@
       <c r="K36" t="n">
         <v>4</v>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2076,12 +2340,19 @@
       <c r="K37" t="n">
         <v>4</v>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2119,12 +2390,19 @@
       <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2162,12 +2440,19 @@
       <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2205,12 +2490,19 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>8</v>
+      </c>
+      <c r="T40" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2248,12 +2540,19 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2291,12 +2590,19 @@
       <c r="K42" t="n">
         <v>3</v>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="n">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2334,12 +2640,19 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="n">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2377,12 +2690,19 @@
       <c r="K44" t="n">
         <v>1</v>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="n">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2420,12 +2740,19 @@
       <c r="K45" t="n">
         <v>0</v>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="n">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2463,12 +2790,19 @@
       <c r="K46" t="n">
         <v>0</v>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="n">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>11</v>
+      </c>
+      <c r="T46" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2506,12 +2840,19 @@
       <c r="K47" t="n">
         <v>1</v>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="n">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>2</v>
+      </c>
+      <c r="T47" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2549,12 +2890,19 @@
       <c r="K48" t="n">
         <v>2</v>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="n">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2592,12 +2940,19 @@
       <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="n">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2635,12 +2990,19 @@
       <c r="K50" t="n">
         <v>0</v>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="n">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>8</v>
+      </c>
+      <c r="T50" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2678,12 +3040,19 @@
       <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="n">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2721,12 +3090,19 @@
       <c r="K52" t="n">
         <v>0</v>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="n">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2764,12 +3140,19 @@
       <c r="K53" t="n">
         <v>0</v>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="n">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>4</v>
+      </c>
+      <c r="T53" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2807,12 +3190,19 @@
       <c r="K54" t="n">
         <v>1</v>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="n">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>8</v>
+      </c>
+      <c r="T54" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2850,12 +3240,19 @@
       <c r="K55" t="n">
         <v>0</v>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="n">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2893,12 +3290,19 @@
       <c r="K56" t="n">
         <v>0</v>
       </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="n">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2936,12 +3340,19 @@
       <c r="K57" t="n">
         <v>3</v>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="n">
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -2979,12 +3390,19 @@
       <c r="K58" t="n">
         <v>5</v>
       </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="n">
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>9</v>
+      </c>
+      <c r="T58" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3022,12 +3440,19 @@
       <c r="K59" t="n">
         <v>0</v>
       </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="n">
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3065,12 +3490,19 @@
       <c r="K60" t="n">
         <v>0</v>
       </c>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="n">
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3108,12 +3540,19 @@
       <c r="K61" t="n">
         <v>0</v>
       </c>
-      <c r="L61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="n">
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3151,12 +3590,19 @@
       <c r="K62" t="n">
         <v>0</v>
       </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="n">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3194,12 +3640,19 @@
       <c r="K63" t="n">
         <v>0</v>
       </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="n">
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>2</v>
+      </c>
+      <c r="T63" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3237,12 +3690,19 @@
       <c r="K64" t="n">
         <v>0</v>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="n">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3280,12 +3740,19 @@
       <c r="K65" t="n">
         <v>0</v>
       </c>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="n">
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3323,12 +3790,19 @@
       <c r="K66" t="n">
         <v>0</v>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="n">
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>2</v>
+      </c>
+      <c r="T66" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3366,12 +3840,19 @@
       <c r="K67" t="n">
         <v>0</v>
       </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="n">
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3409,12 +3890,19 @@
       <c r="K68" t="n">
         <v>0</v>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="n">
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3452,12 +3940,19 @@
       <c r="K69" t="n">
         <v>0</v>
       </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="n">
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3495,12 +3990,19 @@
       <c r="K70" t="n">
         <v>0</v>
       </c>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="n">
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>3</v>
+      </c>
+      <c r="T70" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3538,12 +4040,19 @@
       <c r="K71" t="n">
         <v>0</v>
       </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="n">
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>2</v>
+      </c>
+      <c r="T71" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3581,12 +4090,19 @@
       <c r="K72" t="n">
         <v>0</v>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="n">
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3624,12 +4140,19 @@
       <c r="K73" t="n">
         <v>0</v>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="n">
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3667,12 +4190,19 @@
       <c r="K74" t="n">
         <v>0</v>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="n">
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3710,12 +4240,19 @@
       <c r="K75" t="n">
         <v>0</v>
       </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="n">
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3753,12 +4290,19 @@
       <c r="K76" t="n">
         <v>0</v>
       </c>
-      <c r="L76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="n">
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>2</v>
+      </c>
+      <c r="T76" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3796,12 +4340,19 @@
       <c r="K77" t="n">
         <v>0</v>
       </c>
-      <c r="L77" t="inlineStr"/>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="n">
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3839,12 +4390,19 @@
       <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="L78" t="inlineStr"/>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="n">
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3882,12 +4440,19 @@
       <c r="K79" t="n">
         <v>0</v>
       </c>
-      <c r="L79" t="inlineStr"/>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="n">
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>16</v>
+      </c>
+      <c r="T79" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3925,12 +4490,19 @@
       <c r="K80" t="n">
         <v>1</v>
       </c>
-      <c r="L80" t="inlineStr"/>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="n">
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>11</v>
+      </c>
+      <c r="T80" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -3968,12 +4540,19 @@
       <c r="K81" t="n">
         <v>0</v>
       </c>
-      <c r="L81" t="inlineStr"/>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="n">
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>14</v>
+      </c>
+      <c r="T81" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4011,12 +4590,19 @@
       <c r="K82" t="n">
         <v>0</v>
       </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="n">
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4054,12 +4640,19 @@
       <c r="K83" t="n">
         <v>0</v>
       </c>
-      <c r="L83" t="inlineStr"/>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="n">
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4097,12 +4690,19 @@
       <c r="K84" t="n">
         <v>0</v>
       </c>
-      <c r="L84" t="inlineStr"/>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="n">
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>4</v>
+      </c>
+      <c r="T84" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4132,9 +4732,7 @@
       <c r="K85" t="n">
         <v>0</v>
       </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
         <v>0</v>
       </c>
@@ -4148,6 +4746,15 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4185,12 +4792,19 @@
       <c r="K86" t="n">
         <v>0</v>
       </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="n">
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4228,12 +4842,19 @@
       <c r="K87" t="n">
         <v>0</v>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="n">
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>3</v>
+      </c>
+      <c r="T87" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4271,12 +4892,19 @@
       <c r="K88" t="n">
         <v>1</v>
       </c>
-      <c r="L88" t="inlineStr"/>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="n">
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4314,12 +4942,19 @@
       <c r="K89" t="n">
         <v>0</v>
       </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="n">
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>13</v>
+      </c>
+      <c r="T89" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4357,12 +4992,19 @@
       <c r="K90" t="n">
         <v>0</v>
       </c>
-      <c r="L90" t="inlineStr"/>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="n">
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="n">
+        <v>6</v>
+      </c>
+      <c r="T90" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4400,12 +5042,19 @@
       <c r="K91" t="n">
         <v>0</v>
       </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="n">
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="n">
+        <v>4</v>
+      </c>
+      <c r="T91" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4443,12 +5092,19 @@
       <c r="K92" t="n">
         <v>0</v>
       </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="n">
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4486,12 +5142,19 @@
       <c r="K93" t="n">
         <v>0</v>
       </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="n">
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4529,12 +5192,19 @@
       <c r="K94" t="n">
         <v>0</v>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="n">
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>2</v>
+      </c>
+      <c r="T94" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4572,12 +5242,19 @@
       <c r="K95" t="n">
         <v>0</v>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="n">
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>3</v>
+      </c>
+      <c r="T95" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4615,12 +5292,19 @@
       <c r="K96" t="n">
         <v>0</v>
       </c>
-      <c r="L96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="n">
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>2</v>
+      </c>
+      <c r="T96" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4658,12 +5342,19 @@
       <c r="K97" t="n">
         <v>0</v>
       </c>
-      <c r="L97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="n">
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4701,12 +5392,19 @@
       <c r="K98" t="n">
         <v>1</v>
       </c>
-      <c r="L98" t="inlineStr"/>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="n">
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4744,12 +5442,19 @@
       <c r="K99" t="n">
         <v>2</v>
       </c>
-      <c r="L99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="n">
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4787,12 +5492,19 @@
       <c r="K100" t="n">
         <v>1</v>
       </c>
-      <c r="L100" t="inlineStr"/>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="n">
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="n">
+        <v>9</v>
+      </c>
+      <c r="T100" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4830,12 +5542,19 @@
       <c r="K101" t="n">
         <v>0</v>
       </c>
-      <c r="L101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="n">
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T101" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4873,12 +5592,19 @@
       <c r="K102" t="n">
         <v>1</v>
       </c>
-      <c r="L102" t="inlineStr"/>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="n">
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="n">
+        <v>14</v>
+      </c>
+      <c r="T102" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4916,12 +5642,19 @@
       <c r="K103" t="n">
         <v>0</v>
       </c>
-      <c r="L103" t="inlineStr"/>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="n">
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="n">
+        <v>2</v>
+      </c>
+      <c r="T103" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -4959,12 +5692,19 @@
       <c r="K104" t="n">
         <v>1</v>
       </c>
-      <c r="L104" t="inlineStr"/>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="n">
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="n">
+        <v>18</v>
+      </c>
+      <c r="T104" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5002,12 +5742,19 @@
       <c r="K105" t="n">
         <v>0</v>
       </c>
-      <c r="L105" t="inlineStr"/>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="n">
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>6</v>
+      </c>
+      <c r="T105" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5045,12 +5792,19 @@
       <c r="K106" t="n">
         <v>0</v>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="n">
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5088,12 +5842,19 @@
       <c r="K107" t="n">
         <v>0</v>
       </c>
-      <c r="L107" t="inlineStr"/>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="n">
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="n">
+        <v>2</v>
+      </c>
+      <c r="T107" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5131,12 +5892,19 @@
       <c r="K108" t="n">
         <v>2</v>
       </c>
-      <c r="L108" t="inlineStr"/>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="n">
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="n">
+        <v>3</v>
+      </c>
+      <c r="T108" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5174,12 +5942,19 @@
       <c r="K109" t="n">
         <v>0</v>
       </c>
-      <c r="L109" t="inlineStr"/>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="n">
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5217,12 +5992,19 @@
       <c r="K110" t="n">
         <v>0</v>
       </c>
-      <c r="L110" t="inlineStr"/>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="n">
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5260,12 +6042,19 @@
       <c r="K111" t="n">
         <v>0</v>
       </c>
-      <c r="L111" t="inlineStr"/>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="n">
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="n">
+        <v>2</v>
+      </c>
+      <c r="T111" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5303,12 +6092,19 @@
       <c r="K112" t="n">
         <v>0</v>
       </c>
-      <c r="L112" t="inlineStr"/>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="n">
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5346,12 +6142,19 @@
       <c r="K113" t="n">
         <v>0</v>
       </c>
-      <c r="L113" t="inlineStr"/>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="n">
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5389,12 +6192,19 @@
       <c r="K114" t="n">
         <v>0</v>
       </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="n">
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="n">
+        <v>1</v>
+      </c>
+      <c r="T114" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5432,12 +6242,19 @@
       <c r="K115" t="n">
         <v>0</v>
       </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="n">
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="n">
+        <v>2</v>
+      </c>
+      <c r="T115" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5475,12 +6292,19 @@
       <c r="K116" t="n">
         <v>0</v>
       </c>
-      <c r="L116" t="inlineStr"/>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="n">
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="n">
+        <v>2</v>
+      </c>
+      <c r="T116" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5518,12 +6342,19 @@
       <c r="K117" t="n">
         <v>0</v>
       </c>
-      <c r="L117" t="inlineStr"/>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="n">
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5561,12 +6392,19 @@
       <c r="K118" t="n">
         <v>0</v>
       </c>
-      <c r="L118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="n">
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="n">
+        <v>2</v>
+      </c>
+      <c r="T118" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5604,12 +6442,19 @@
       <c r="K119" t="n">
         <v>0</v>
       </c>
-      <c r="L119" t="inlineStr"/>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="n">
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5647,12 +6492,19 @@
       <c r="K120" t="n">
         <v>0</v>
       </c>
-      <c r="L120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="n">
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="n">
+        <v>4</v>
+      </c>
+      <c r="T120" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5690,12 +6542,19 @@
       <c r="K121" t="n">
         <v>0</v>
       </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="n">
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="n">
+        <v>8</v>
+      </c>
+      <c r="T121" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5733,12 +6592,19 @@
       <c r="K122" t="n">
         <v>0</v>
       </c>
-      <c r="L122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="n">
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5776,12 +6642,19 @@
       <c r="K123" t="n">
         <v>0</v>
       </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="n">
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5819,12 +6692,19 @@
       <c r="K124" t="n">
         <v>0</v>
       </c>
-      <c r="L124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="n">
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5862,12 +6742,19 @@
       <c r="K125" t="n">
         <v>0</v>
       </c>
-      <c r="L125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="n">
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5905,12 +6792,19 @@
       <c r="K126" t="n">
         <v>0</v>
       </c>
-      <c r="L126" t="inlineStr"/>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="n">
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="n">
+        <v>8</v>
+      </c>
+      <c r="T126" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5948,12 +6842,19 @@
       <c r="K127" t="n">
         <v>1</v>
       </c>
-      <c r="L127" t="inlineStr"/>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="n">
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="n">
+        <v>4</v>
+      </c>
+      <c r="T127" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -5991,12 +6892,19 @@
       <c r="K128" t="n">
         <v>1</v>
       </c>
-      <c r="L128" t="inlineStr"/>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="n">
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="n">
+        <v>2</v>
+      </c>
+      <c r="T128" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6034,12 +6942,19 @@
       <c r="K129" t="n">
         <v>0</v>
       </c>
-      <c r="L129" t="inlineStr"/>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="n">
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="n">
+        <v>3</v>
+      </c>
+      <c r="T129" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6077,12 +6992,19 @@
       <c r="K130" t="n">
         <v>0</v>
       </c>
-      <c r="L130" t="inlineStr"/>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="n">
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="n">
+        <v>1</v>
+      </c>
+      <c r="T130" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6120,12 +7042,19 @@
       <c r="K131" t="n">
         <v>0</v>
       </c>
-      <c r="L131" t="inlineStr"/>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="n">
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6163,12 +7092,19 @@
       <c r="K132" t="n">
         <v>0</v>
       </c>
-      <c r="L132" t="inlineStr"/>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="n">
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6206,12 +7142,19 @@
       <c r="K133" t="n">
         <v>3</v>
       </c>
-      <c r="L133" t="inlineStr"/>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="n">
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6249,12 +7192,19 @@
       <c r="K134" t="n">
         <v>1</v>
       </c>
-      <c r="L134" t="inlineStr"/>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="n">
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="n">
+        <v>4</v>
+      </c>
+      <c r="T134" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6292,12 +7242,19 @@
       <c r="K135" t="n">
         <v>0</v>
       </c>
-      <c r="L135" t="inlineStr"/>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="n">
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="n">
+        <v>2</v>
+      </c>
+      <c r="T135" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6335,12 +7292,19 @@
       <c r="K136" t="n">
         <v>1</v>
       </c>
-      <c r="L136" t="inlineStr"/>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="n">
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="n">
+        <v>3</v>
+      </c>
+      <c r="T136" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6378,12 +7342,19 @@
       <c r="K137" t="n">
         <v>0</v>
       </c>
-      <c r="L137" t="inlineStr"/>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="n">
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="n">
+        <v>2</v>
+      </c>
+      <c r="T137" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6421,12 +7392,19 @@
       <c r="K138" t="n">
         <v>0</v>
       </c>
-      <c r="L138" t="inlineStr"/>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="n">
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6464,12 +7442,19 @@
       <c r="K139" t="n">
         <v>0</v>
       </c>
-      <c r="L139" t="inlineStr"/>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="n">
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="n">
+        <v>1</v>
+      </c>
+      <c r="T139" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6507,12 +7492,19 @@
       <c r="K140" t="n">
         <v>0</v>
       </c>
-      <c r="L140" t="inlineStr"/>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="n">
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6550,12 +7542,19 @@
       <c r="K141" t="n">
         <v>0</v>
       </c>
-      <c r="L141" t="inlineStr"/>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="n">
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="n">
+        <v>1</v>
+      </c>
+      <c r="T141" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6593,12 +7592,19 @@
       <c r="K142" t="n">
         <v>0</v>
       </c>
-      <c r="L142" t="inlineStr"/>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="n">
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="n">
+        <v>1</v>
+      </c>
+      <c r="T142" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6636,12 +7642,19 @@
       <c r="K143" t="n">
         <v>0</v>
       </c>
-      <c r="L143" t="inlineStr"/>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="n">
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="n">
+        <v>1</v>
+      </c>
+      <c r="T143" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6679,12 +7692,19 @@
       <c r="K144" t="n">
         <v>0</v>
       </c>
-      <c r="L144" t="inlineStr"/>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="n">
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="n">
+        <v>2</v>
+      </c>
+      <c r="T144" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6722,12 +7742,19 @@
       <c r="K145" t="n">
         <v>0</v>
       </c>
-      <c r="L145" t="inlineStr"/>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="n">
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6765,12 +7792,19 @@
       <c r="K146" t="n">
         <v>0</v>
       </c>
-      <c r="L146" t="inlineStr"/>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="n">
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="n">
+        <v>6</v>
+      </c>
+      <c r="T146" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6808,12 +7842,19 @@
       <c r="K147" t="n">
         <v>3</v>
       </c>
-      <c r="L147" t="inlineStr"/>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="n">
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="n">
+        <v>2</v>
+      </c>
+      <c r="T147" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6851,12 +7892,19 @@
       <c r="K148" t="n">
         <v>0</v>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="n">
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6894,12 +7942,19 @@
       <c r="K149" t="n">
         <v>0</v>
       </c>
-      <c r="L149" t="inlineStr"/>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="n">
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6937,12 +7992,19 @@
       <c r="K150" t="n">
         <v>0</v>
       </c>
-      <c r="L150" t="inlineStr"/>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="n">
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="n">
+        <v>5</v>
+      </c>
+      <c r="T150" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -6980,12 +8042,19 @@
       <c r="K151" t="n">
         <v>2</v>
       </c>
-      <c r="L151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="n">
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="n">
+        <v>11</v>
+      </c>
+      <c r="T151" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7023,12 +8092,19 @@
       <c r="K152" t="n">
         <v>0</v>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="n">
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7066,12 +8142,19 @@
       <c r="K153" t="n">
         <v>1</v>
       </c>
-      <c r="L153" t="inlineStr"/>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="n">
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="n">
+        <v>6</v>
+      </c>
+      <c r="T153" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7109,12 +8192,19 @@
       <c r="K154" t="n">
         <v>5</v>
       </c>
-      <c r="L154" t="inlineStr"/>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="n">
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7152,12 +8242,19 @@
       <c r="K155" t="n">
         <v>1</v>
       </c>
-      <c r="L155" t="inlineStr"/>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="n">
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="n">
+        <v>13</v>
+      </c>
+      <c r="T155" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7195,12 +8292,19 @@
       <c r="K156" t="n">
         <v>3</v>
       </c>
-      <c r="L156" t="inlineStr"/>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="n">
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="n">
+        <v>1</v>
+      </c>
+      <c r="T156" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7238,12 +8342,19 @@
       <c r="K157" t="n">
         <v>0</v>
       </c>
-      <c r="L157" t="inlineStr"/>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="n">
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7281,12 +8392,19 @@
       <c r="K158" t="n">
         <v>5</v>
       </c>
-      <c r="L158" t="inlineStr"/>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="n">
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7324,12 +8442,19 @@
       <c r="K159" t="n">
         <v>0</v>
       </c>
-      <c r="L159" t="inlineStr"/>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="n">
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="n">
+        <v>1</v>
+      </c>
+      <c r="T159" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7367,12 +8492,19 @@
       <c r="K160" t="n">
         <v>1</v>
       </c>
-      <c r="L160" t="inlineStr"/>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="n">
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="n">
+        <v>3</v>
+      </c>
+      <c r="T160" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7410,12 +8542,19 @@
       <c r="K161" t="n">
         <v>0</v>
       </c>
-      <c r="L161" t="inlineStr"/>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="n">
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="n">
+        <v>7</v>
+      </c>
+      <c r="T161" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7453,12 +8592,19 @@
       <c r="K162" t="n">
         <v>0</v>
       </c>
-      <c r="L162" t="inlineStr"/>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="n">
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="n">
+        <v>4</v>
+      </c>
+      <c r="T162" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7496,12 +8642,19 @@
       <c r="K163" t="n">
         <v>0</v>
       </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="n">
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="n">
+        <v>4</v>
+      </c>
+      <c r="T163" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7539,12 +8692,19 @@
       <c r="K164" t="n">
         <v>1</v>
       </c>
-      <c r="L164" t="inlineStr"/>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="n">
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="n">
+        <v>3</v>
+      </c>
+      <c r="T164" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7582,12 +8742,19 @@
       <c r="K165" t="n">
         <v>0</v>
       </c>
-      <c r="L165" t="inlineStr"/>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="n">
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="n">
+        <v>5</v>
+      </c>
+      <c r="T165" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7625,12 +8792,19 @@
       <c r="K166" t="n">
         <v>0</v>
       </c>
-      <c r="L166" t="inlineStr"/>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="n">
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="n">
+        <v>3</v>
+      </c>
+      <c r="T166" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7668,12 +8842,19 @@
       <c r="K167" t="n">
         <v>0</v>
       </c>
-      <c r="L167" t="inlineStr"/>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="n">
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7711,12 +8892,19 @@
       <c r="K168" t="n">
         <v>0</v>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="n">
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="n">
+        <v>3</v>
+      </c>
+      <c r="T168" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7754,12 +8942,19 @@
       <c r="K169" t="n">
         <v>0</v>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="n">
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="n">
+        <v>1</v>
+      </c>
+      <c r="T169" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7797,12 +8992,19 @@
       <c r="K170" t="n">
         <v>0</v>
       </c>
-      <c r="L170" t="inlineStr"/>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="n">
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="n">
+        <v>2</v>
+      </c>
+      <c r="T170" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7840,12 +9042,19 @@
       <c r="K171" t="n">
         <v>0</v>
       </c>
-      <c r="L171" t="inlineStr"/>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="n">
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7883,12 +9092,19 @@
       <c r="K172" t="n">
         <v>0</v>
       </c>
-      <c r="L172" t="inlineStr"/>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="n">
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="n">
+        <v>7</v>
+      </c>
+      <c r="T172" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7926,12 +9142,19 @@
       <c r="K173" t="n">
         <v>0</v>
       </c>
-      <c r="L173" t="inlineStr"/>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="n">
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -7969,12 +9192,19 @@
       <c r="K174" t="n">
         <v>1</v>
       </c>
-      <c r="L174" t="inlineStr"/>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="n">
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="n">
+        <v>11</v>
+      </c>
+      <c r="T174" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8012,12 +9242,19 @@
       <c r="K175" t="n">
         <v>0</v>
       </c>
-      <c r="L175" t="inlineStr"/>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="n">
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="n">
+        <v>4</v>
+      </c>
+      <c r="T175" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8055,12 +9292,19 @@
       <c r="K176" t="n">
         <v>0</v>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="n">
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8098,12 +9342,19 @@
       <c r="K177" t="n">
         <v>0</v>
       </c>
-      <c r="L177" t="inlineStr"/>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="n">
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8141,12 +9392,19 @@
       <c r="K178" t="n">
         <v>0</v>
       </c>
-      <c r="L178" t="inlineStr"/>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="n">
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8184,12 +9442,19 @@
       <c r="K179" t="n">
         <v>0</v>
       </c>
-      <c r="L179" t="inlineStr"/>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="n">
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="n">
+        <v>3</v>
+      </c>
+      <c r="T179" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8227,12 +9492,19 @@
       <c r="K180" t="n">
         <v>0</v>
       </c>
-      <c r="L180" t="inlineStr"/>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="n">
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8270,12 +9542,19 @@
       <c r="K181" t="n">
         <v>0</v>
       </c>
-      <c r="L181" t="inlineStr"/>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="n">
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="n">
+        <v>5</v>
+      </c>
+      <c r="T181" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8313,12 +9592,19 @@
       <c r="K182" t="n">
         <v>0</v>
       </c>
-      <c r="L182" t="inlineStr"/>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="n">
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="n">
+        <v>14</v>
+      </c>
+      <c r="T182" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8356,12 +9642,19 @@
       <c r="K183" t="n">
         <v>0</v>
       </c>
-      <c r="L183" t="inlineStr"/>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="n">
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="n">
+        <v>2</v>
+      </c>
+      <c r="T183" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8399,12 +9692,19 @@
       <c r="K184" t="n">
         <v>0</v>
       </c>
-      <c r="L184" t="inlineStr"/>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="n">
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="n">
+        <v>4</v>
+      </c>
+      <c r="T184" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8442,12 +9742,19 @@
       <c r="K185" t="n">
         <v>0</v>
       </c>
-      <c r="L185" t="inlineStr"/>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="n">
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="n">
+        <v>7</v>
+      </c>
+      <c r="T185" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8485,12 +9792,19 @@
       <c r="K186" t="n">
         <v>0</v>
       </c>
-      <c r="L186" t="inlineStr"/>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="n">
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="n">
+        <v>1</v>
+      </c>
+      <c r="T186" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8528,12 +9842,19 @@
       <c r="K187" t="n">
         <v>0</v>
       </c>
-      <c r="L187" t="inlineStr"/>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="n">
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="n">
+        <v>1</v>
+      </c>
+      <c r="T187" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8571,12 +9892,19 @@
       <c r="K188" t="n">
         <v>0</v>
       </c>
-      <c r="L188" t="inlineStr"/>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="n">
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="n">
+        <v>6</v>
+      </c>
+      <c r="T188" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8614,12 +9942,19 @@
       <c r="K189" t="n">
         <v>0</v>
       </c>
-      <c r="L189" t="inlineStr"/>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="n">
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="n">
+        <v>2</v>
+      </c>
+      <c r="T189" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8657,12 +9992,19 @@
       <c r="K190" t="n">
         <v>0</v>
       </c>
-      <c r="L190" t="inlineStr"/>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="n">
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="n">
+        <v>1</v>
+      </c>
+      <c r="T190" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8700,12 +10042,19 @@
       <c r="K191" t="n">
         <v>0</v>
       </c>
-      <c r="L191" t="inlineStr"/>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="n">
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="n">
+        <v>1</v>
+      </c>
+      <c r="T191" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8743,12 +10092,19 @@
       <c r="K192" t="n">
         <v>1</v>
       </c>
-      <c r="L192" t="inlineStr"/>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="n">
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="n">
+        <v>2</v>
+      </c>
+      <c r="T192" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8786,12 +10142,19 @@
       <c r="K193" t="n">
         <v>0</v>
       </c>
-      <c r="L193" t="inlineStr"/>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="n">
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8829,12 +10192,19 @@
       <c r="K194" t="n">
         <v>1</v>
       </c>
-      <c r="L194" t="inlineStr"/>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="n">
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="n">
+        <v>4</v>
+      </c>
+      <c r="T194" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8872,12 +10242,19 @@
       <c r="K195" t="n">
         <v>1</v>
       </c>
-      <c r="L195" t="inlineStr"/>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="n">
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="n">
+        <v>8</v>
+      </c>
+      <c r="T195" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8915,12 +10292,19 @@
       <c r="K196" t="n">
         <v>3</v>
       </c>
-      <c r="L196" t="inlineStr"/>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="n">
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -8958,12 +10342,19 @@
       <c r="K197" t="n">
         <v>0</v>
       </c>
-      <c r="L197" t="inlineStr"/>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="n">
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="n">
+        <v>3</v>
+      </c>
+      <c r="T197" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9001,12 +10392,19 @@
       <c r="K198" t="n">
         <v>0</v>
       </c>
-      <c r="L198" t="inlineStr"/>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="n">
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9044,12 +10442,19 @@
       <c r="K199" t="n">
         <v>1</v>
       </c>
-      <c r="L199" t="inlineStr"/>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="n">
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="n">
+        <v>0</v>
+      </c>
+      <c r="T199" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9087,12 +10492,19 @@
       <c r="K200" t="n">
         <v>0</v>
       </c>
-      <c r="L200" t="inlineStr"/>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="n">
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9130,12 +10542,19 @@
       <c r="K201" t="n">
         <v>0</v>
       </c>
-      <c r="L201" t="inlineStr"/>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="n">
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="n">
+        <v>1</v>
+      </c>
+      <c r="T201" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9173,12 +10592,19 @@
       <c r="K202" t="n">
         <v>0</v>
       </c>
-      <c r="L202" t="inlineStr"/>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="n">
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="n">
+        <v>2</v>
+      </c>
+      <c r="T202" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9216,12 +10642,19 @@
       <c r="K203" t="n">
         <v>0</v>
       </c>
-      <c r="L203" t="inlineStr"/>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="n">
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9259,12 +10692,19 @@
       <c r="K204" t="n">
         <v>1</v>
       </c>
-      <c r="L204" t="inlineStr"/>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="n">
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="n">
+        <v>1</v>
+      </c>
+      <c r="T204" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9302,12 +10742,19 @@
       <c r="K205" t="n">
         <v>0</v>
       </c>
-      <c r="L205" t="inlineStr"/>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="n">
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="n">
+        <v>2</v>
+      </c>
+      <c r="T205" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9345,12 +10792,19 @@
       <c r="K206" t="n">
         <v>0</v>
       </c>
-      <c r="L206" t="inlineStr"/>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="n">
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="n">
+        <v>0</v>
+      </c>
+      <c r="T206" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9388,12 +10842,19 @@
       <c r="K207" t="n">
         <v>1</v>
       </c>
-      <c r="L207" t="inlineStr"/>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="n">
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="n">
+        <v>3</v>
+      </c>
+      <c r="T207" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9431,12 +10892,19 @@
       <c r="K208" t="n">
         <v>4</v>
       </c>
-      <c r="L208" t="inlineStr"/>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="n">
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="n">
+        <v>5</v>
+      </c>
+      <c r="T208" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9474,12 +10942,19 @@
       <c r="K209" t="n">
         <v>0</v>
       </c>
-      <c r="L209" t="inlineStr"/>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="n">
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="n">
+        <v>7</v>
+      </c>
+      <c r="T209" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9517,12 +10992,19 @@
       <c r="K210" t="n">
         <v>0</v>
       </c>
-      <c r="L210" t="inlineStr"/>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="n">
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="n">
+        <v>1</v>
+      </c>
+      <c r="T210" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9560,12 +11042,19 @@
       <c r="K211" t="n">
         <v>0</v>
       </c>
-      <c r="L211" t="inlineStr"/>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="n">
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="n">
+        <v>2</v>
+      </c>
+      <c r="T211" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9603,12 +11092,19 @@
       <c r="K212" t="n">
         <v>0</v>
       </c>
-      <c r="L212" t="inlineStr"/>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="n">
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9646,12 +11142,19 @@
       <c r="K213" t="n">
         <v>0</v>
       </c>
-      <c r="L213" t="inlineStr"/>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="n">
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="n">
+        <v>1</v>
+      </c>
+      <c r="T213" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9689,12 +11192,19 @@
       <c r="K214" t="n">
         <v>0</v>
       </c>
-      <c r="L214" t="inlineStr"/>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="n">
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="n">
+        <v>6</v>
+      </c>
+      <c r="T214" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9732,12 +11242,19 @@
       <c r="K215" t="n">
         <v>0</v>
       </c>
-      <c r="L215" t="inlineStr"/>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="n">
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="n">
+        <v>4</v>
+      </c>
+      <c r="T215" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9775,12 +11292,19 @@
       <c r="K216" t="n">
         <v>0</v>
       </c>
-      <c r="L216" t="inlineStr"/>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="n">
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9818,12 +11342,19 @@
       <c r="K217" t="n">
         <v>0</v>
       </c>
-      <c r="L217" t="inlineStr"/>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="n">
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="n">
+        <v>1</v>
+      </c>
+      <c r="T217" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9861,12 +11392,19 @@
       <c r="K218" t="n">
         <v>2</v>
       </c>
-      <c r="L218" t="inlineStr"/>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="n">
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="n">
+        <v>7</v>
+      </c>
+      <c r="T218" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9904,12 +11442,19 @@
       <c r="K219" t="n">
         <v>0</v>
       </c>
-      <c r="L219" t="inlineStr"/>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="n">
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
+      <c r="S219" t="n">
+        <v>11</v>
+      </c>
+      <c r="T219" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9947,12 +11492,19 @@
       <c r="K220" t="n">
         <v>2</v>
       </c>
-      <c r="L220" t="inlineStr"/>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="n">
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
+      <c r="S220" t="n">
+        <v>6</v>
+      </c>
+      <c r="T220" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -9990,12 +11542,19 @@
       <c r="K221" t="n">
         <v>0</v>
       </c>
-      <c r="L221" t="inlineStr"/>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="n">
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="n">
+        <v>8</v>
+      </c>
+      <c r="T221" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10033,12 +11592,19 @@
       <c r="K222" t="n">
         <v>0</v>
       </c>
-      <c r="L222" t="inlineStr"/>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="n">
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+      <c r="S222" t="n">
+        <v>1</v>
+      </c>
+      <c r="T222" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10076,12 +11642,19 @@
       <c r="K223" t="n">
         <v>0</v>
       </c>
-      <c r="L223" t="inlineStr"/>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="n">
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
+      <c r="S223" t="n">
+        <v>6</v>
+      </c>
+      <c r="T223" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10119,12 +11692,19 @@
       <c r="K224" t="n">
         <v>0</v>
       </c>
-      <c r="L224" t="inlineStr"/>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="n">
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
+      <c r="S224" t="n">
+        <v>1</v>
+      </c>
+      <c r="T224" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10162,12 +11742,19 @@
       <c r="K225" t="n">
         <v>0</v>
       </c>
-      <c r="L225" t="inlineStr"/>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="n">
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="n">
+        <v>4</v>
+      </c>
+      <c r="T225" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10205,12 +11792,19 @@
       <c r="K226" t="n">
         <v>0</v>
       </c>
-      <c r="L226" t="inlineStr"/>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="n">
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="n">
+        <v>4</v>
+      </c>
+      <c r="T226" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10248,12 +11842,19 @@
       <c r="K227" t="n">
         <v>0</v>
       </c>
-      <c r="L227" t="inlineStr"/>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="n">
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="n">
+        <v>5</v>
+      </c>
+      <c r="T227" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10291,12 +11892,19 @@
       <c r="K228" t="n">
         <v>0</v>
       </c>
-      <c r="L228" t="inlineStr"/>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="n">
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="n">
+        <v>5</v>
+      </c>
+      <c r="T228" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10334,12 +11942,19 @@
       <c r="K229" t="n">
         <v>2</v>
       </c>
-      <c r="L229" t="inlineStr"/>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="n">
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="n">
+        <v>14</v>
+      </c>
+      <c r="T229" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10377,12 +11992,19 @@
       <c r="K230" t="n">
         <v>0</v>
       </c>
-      <c r="L230" t="inlineStr"/>
+      <c r="L230" t="n">
+        <v>0</v>
+      </c>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="n">
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="n">
+        <v>10</v>
+      </c>
+      <c r="T230" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10420,12 +12042,19 @@
       <c r="K231" t="n">
         <v>0</v>
       </c>
-      <c r="L231" t="inlineStr"/>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="n">
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10463,12 +12092,19 @@
       <c r="K232" t="n">
         <v>0</v>
       </c>
-      <c r="L232" t="inlineStr"/>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="n">
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="n">
+        <v>12</v>
+      </c>
+      <c r="T232" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10506,12 +12142,19 @@
       <c r="K233" t="n">
         <v>1</v>
       </c>
-      <c r="L233" t="inlineStr"/>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="n">
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="n">
+        <v>1</v>
+      </c>
+      <c r="T233" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10549,12 +12192,19 @@
       <c r="K234" t="n">
         <v>0</v>
       </c>
-      <c r="L234" t="inlineStr"/>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="n">
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="n">
+        <v>0</v>
+      </c>
+      <c r="T234" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10592,12 +12242,19 @@
       <c r="K235" t="n">
         <v>0</v>
       </c>
-      <c r="L235" t="inlineStr"/>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="n">
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
+      <c r="S235" t="n">
+        <v>9</v>
+      </c>
+      <c r="T235" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10635,12 +12292,19 @@
       <c r="K236" t="n">
         <v>0</v>
       </c>
-      <c r="L236" t="inlineStr"/>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
       <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="n">
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
+      <c r="S236" t="n">
+        <v>6</v>
+      </c>
+      <c r="T236" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10678,12 +12342,19 @@
       <c r="K237" t="n">
         <v>1</v>
       </c>
-      <c r="L237" t="inlineStr"/>
+      <c r="L237" t="n">
+        <v>0</v>
+      </c>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="n">
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="n">
+        <v>12</v>
+      </c>
+      <c r="T237" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10721,12 +12392,19 @@
       <c r="K238" t="n">
         <v>0</v>
       </c>
-      <c r="L238" t="inlineStr"/>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="n">
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
+      <c r="S238" t="n">
+        <v>14</v>
+      </c>
+      <c r="T238" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10764,12 +12442,19 @@
       <c r="K239" t="n">
         <v>0</v>
       </c>
-      <c r="L239" t="inlineStr"/>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="n">
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="n">
+        <v>2</v>
+      </c>
+      <c r="T239" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10807,12 +12492,19 @@
       <c r="K240" t="n">
         <v>0</v>
       </c>
-      <c r="L240" t="inlineStr"/>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="n">
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr"/>
+      <c r="S240" t="n">
+        <v>6</v>
+      </c>
+      <c r="T240" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10850,12 +12542,19 @@
       <c r="K241" t="n">
         <v>0</v>
       </c>
-      <c r="L241" t="inlineStr"/>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="n">
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
+      <c r="S241" t="n">
+        <v>0</v>
+      </c>
+      <c r="T241" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10893,12 +12592,19 @@
       <c r="K242" t="n">
         <v>0</v>
       </c>
-      <c r="L242" t="inlineStr"/>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="n">
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr"/>
+      <c r="S242" t="n">
+        <v>0</v>
+      </c>
+      <c r="T242" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10936,12 +12642,19 @@
       <c r="K243" t="n">
         <v>0</v>
       </c>
-      <c r="L243" t="inlineStr"/>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="n">
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -10979,12 +12692,19 @@
       <c r="K244" t="n">
         <v>0</v>
       </c>
-      <c r="L244" t="inlineStr"/>
+      <c r="L244" t="n">
+        <v>0</v>
+      </c>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="n">
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
+      <c r="S244" t="n">
+        <v>6</v>
+      </c>
+      <c r="T244" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11022,12 +12742,19 @@
       <c r="K245" t="n">
         <v>0</v>
       </c>
-      <c r="L245" t="inlineStr"/>
+      <c r="L245" t="n">
+        <v>0</v>
+      </c>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="n">
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="n">
+        <v>0</v>
+      </c>
+      <c r="T245" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11065,12 +12792,19 @@
       <c r="K246" t="n">
         <v>3</v>
       </c>
-      <c r="L246" t="inlineStr"/>
+      <c r="L246" t="n">
+        <v>0</v>
+      </c>
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="n">
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="n">
+        <v>0</v>
+      </c>
+      <c r="T246" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11108,12 +12842,19 @@
       <c r="K247" t="n">
         <v>0</v>
       </c>
-      <c r="L247" t="inlineStr"/>
+      <c r="L247" t="n">
+        <v>0</v>
+      </c>
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="n">
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
+      <c r="S247" t="n">
+        <v>3</v>
+      </c>
+      <c r="T247" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11151,12 +12892,19 @@
       <c r="K248" t="n">
         <v>0</v>
       </c>
-      <c r="L248" t="inlineStr"/>
+      <c r="L248" t="n">
+        <v>0</v>
+      </c>
       <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr"/>
-      <c r="Q248" t="n">
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
+      <c r="S248" t="n">
+        <v>0</v>
+      </c>
+      <c r="T248" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11194,12 +12942,19 @@
       <c r="K249" t="n">
         <v>0</v>
       </c>
-      <c r="L249" t="inlineStr"/>
+      <c r="L249" t="n">
+        <v>0</v>
+      </c>
       <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="n">
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
+      <c r="S249" t="n">
+        <v>0</v>
+      </c>
+      <c r="T249" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11237,12 +12992,19 @@
       <c r="K250" t="n">
         <v>0</v>
       </c>
-      <c r="L250" t="inlineStr"/>
+      <c r="L250" t="n">
+        <v>0</v>
+      </c>
       <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
       <c r="P250" t="inlineStr"/>
-      <c r="Q250" t="n">
+      <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
+      <c r="S250" t="n">
+        <v>4</v>
+      </c>
+      <c r="T250" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11280,12 +13042,19 @@
       <c r="K251" t="n">
         <v>0</v>
       </c>
-      <c r="L251" t="inlineStr"/>
+      <c r="L251" t="n">
+        <v>0</v>
+      </c>
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
       <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="n">
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
+      <c r="S251" t="n">
+        <v>3</v>
+      </c>
+      <c r="T251" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11323,12 +13092,19 @@
       <c r="K252" t="n">
         <v>0</v>
       </c>
-      <c r="L252" t="inlineStr"/>
+      <c r="L252" t="n">
+        <v>0</v>
+      </c>
       <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr"/>
-      <c r="Q252" t="n">
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
+      <c r="S252" t="n">
+        <v>0</v>
+      </c>
+      <c r="T252" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11366,12 +13142,19 @@
       <c r="K253" t="n">
         <v>0</v>
       </c>
-      <c r="L253" t="inlineStr"/>
+      <c r="L253" t="n">
+        <v>0</v>
+      </c>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="n">
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
+      <c r="S253" t="n">
+        <v>1</v>
+      </c>
+      <c r="T253" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11409,12 +13192,19 @@
       <c r="K254" t="n">
         <v>0</v>
       </c>
-      <c r="L254" t="inlineStr"/>
+      <c r="L254" t="n">
+        <v>0</v>
+      </c>
       <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr"/>
-      <c r="Q254" t="n">
+      <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
+      <c r="S254" t="n">
+        <v>0</v>
+      </c>
+      <c r="T254" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11452,12 +13242,19 @@
       <c r="K255" t="n">
         <v>0</v>
       </c>
-      <c r="L255" t="inlineStr"/>
+      <c r="L255" t="n">
+        <v>0</v>
+      </c>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="n">
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
+      <c r="S255" t="n">
+        <v>0</v>
+      </c>
+      <c r="T255" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11495,12 +13292,19 @@
       <c r="K256" t="n">
         <v>4</v>
       </c>
-      <c r="L256" t="inlineStr"/>
+      <c r="L256" t="n">
+        <v>0</v>
+      </c>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="n">
+      <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
+      <c r="S256" t="n">
+        <v>0</v>
+      </c>
+      <c r="T256" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11538,12 +13342,19 @@
       <c r="K257" t="n">
         <v>0</v>
       </c>
-      <c r="L257" t="inlineStr"/>
+      <c r="L257" t="n">
+        <v>0</v>
+      </c>
       <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr"/>
-      <c r="Q257" t="n">
+      <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
+      <c r="S257" t="n">
+        <v>2</v>
+      </c>
+      <c r="T257" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11581,12 +13392,19 @@
       <c r="K258" t="n">
         <v>0</v>
       </c>
-      <c r="L258" t="inlineStr"/>
+      <c r="L258" t="n">
+        <v>0</v>
+      </c>
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr"/>
-      <c r="Q258" t="n">
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11624,12 +13442,19 @@
       <c r="K259" t="n">
         <v>0</v>
       </c>
-      <c r="L259" t="inlineStr"/>
+      <c r="L259" t="n">
+        <v>0</v>
+      </c>
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="n">
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
+      <c r="S259" t="n">
+        <v>4</v>
+      </c>
+      <c r="T259" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11667,12 +13492,19 @@
       <c r="K260" t="n">
         <v>0</v>
       </c>
-      <c r="L260" t="inlineStr"/>
+      <c r="L260" t="n">
+        <v>0</v>
+      </c>
       <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="n">
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
+      <c r="S260" t="n">
+        <v>3</v>
+      </c>
+      <c r="T260" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11710,12 +13542,19 @@
       <c r="K261" t="n">
         <v>0</v>
       </c>
-      <c r="L261" t="inlineStr"/>
+      <c r="L261" t="n">
+        <v>0</v>
+      </c>
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="n">
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="n">
+        <v>11</v>
+      </c>
+      <c r="T261" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11753,12 +13592,19 @@
       <c r="K262" t="n">
         <v>3</v>
       </c>
-      <c r="L262" t="inlineStr"/>
+      <c r="L262" t="n">
+        <v>1</v>
+      </c>
       <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr"/>
-      <c r="Q262" t="n">
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
+      <c r="S262" t="n">
+        <v>0</v>
+      </c>
+      <c r="T262" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11796,12 +13642,19 @@
       <c r="K263" t="n">
         <v>0</v>
       </c>
-      <c r="L263" t="inlineStr"/>
+      <c r="L263" t="n">
+        <v>0</v>
+      </c>
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="n">
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
+      <c r="S263" t="n">
+        <v>0</v>
+      </c>
+      <c r="T263" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11839,12 +13692,19 @@
       <c r="K264" t="n">
         <v>0</v>
       </c>
-      <c r="L264" t="inlineStr"/>
+      <c r="L264" t="n">
+        <v>0</v>
+      </c>
       <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr"/>
-      <c r="Q264" t="n">
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
+      <c r="S264" t="n">
+        <v>3</v>
+      </c>
+      <c r="T264" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11882,12 +13742,19 @@
       <c r="K265" t="n">
         <v>0</v>
       </c>
-      <c r="L265" t="inlineStr"/>
+      <c r="L265" t="n">
+        <v>0</v>
+      </c>
       <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="n">
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
+      <c r="S265" t="n">
+        <v>7</v>
+      </c>
+      <c r="T265" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11925,12 +13792,19 @@
       <c r="K266" t="n">
         <v>0</v>
       </c>
-      <c r="L266" t="inlineStr"/>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
       <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="n">
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+      <c r="S266" t="n">
+        <v>1</v>
+      </c>
+      <c r="T266" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -11968,12 +13842,19 @@
       <c r="K267" t="n">
         <v>2</v>
       </c>
-      <c r="L267" t="inlineStr"/>
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
       <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="inlineStr"/>
-      <c r="Q267" t="n">
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
+      <c r="S267" t="n">
+        <v>5</v>
+      </c>
+      <c r="T267" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12011,12 +13892,19 @@
       <c r="K268" t="n">
         <v>0</v>
       </c>
-      <c r="L268" t="inlineStr"/>
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
       <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr"/>
-      <c r="Q268" t="n">
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
+      <c r="S268" t="n">
+        <v>4</v>
+      </c>
+      <c r="T268" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12054,12 +13942,19 @@
       <c r="K269" t="n">
         <v>0</v>
       </c>
-      <c r="L269" t="inlineStr"/>
+      <c r="L269" t="n">
+        <v>0</v>
+      </c>
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr"/>
       <c r="P269" t="inlineStr"/>
-      <c r="Q269" t="n">
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
+      <c r="S269" t="n">
+        <v>6</v>
+      </c>
+      <c r="T269" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12097,12 +13992,19 @@
       <c r="K270" t="n">
         <v>0</v>
       </c>
-      <c r="L270" t="inlineStr"/>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
       <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr"/>
-      <c r="Q270" t="n">
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+      <c r="S270" t="n">
+        <v>3</v>
+      </c>
+      <c r="T270" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12140,12 +14042,19 @@
       <c r="K271" t="n">
         <v>1</v>
       </c>
-      <c r="L271" t="inlineStr"/>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
       <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr"/>
-      <c r="Q271" t="n">
+      <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
+      <c r="S271" t="n">
+        <v>4</v>
+      </c>
+      <c r="T271" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12183,12 +14092,19 @@
       <c r="K272" t="n">
         <v>0</v>
       </c>
-      <c r="L272" t="inlineStr"/>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
       <c r="M272" t="inlineStr"/>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr"/>
-      <c r="Q272" t="n">
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
+      <c r="S272" t="n">
+        <v>0</v>
+      </c>
+      <c r="T272" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12226,12 +14142,19 @@
       <c r="K273" t="n">
         <v>0</v>
       </c>
-      <c r="L273" t="inlineStr"/>
+      <c r="L273" t="n">
+        <v>0</v>
+      </c>
       <c r="M273" t="inlineStr"/>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="n">
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
+      <c r="S273" t="n">
+        <v>2</v>
+      </c>
+      <c r="T273" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12269,12 +14192,19 @@
       <c r="K274" t="n">
         <v>0</v>
       </c>
-      <c r="L274" t="inlineStr"/>
+      <c r="L274" t="n">
+        <v>0</v>
+      </c>
       <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr"/>
-      <c r="Q274" t="n">
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
+      <c r="S274" t="n">
+        <v>3</v>
+      </c>
+      <c r="T274" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12312,12 +14242,19 @@
       <c r="K275" t="n">
         <v>0</v>
       </c>
-      <c r="L275" t="inlineStr"/>
+      <c r="L275" t="n">
+        <v>0</v>
+      </c>
       <c r="M275" t="inlineStr"/>
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr"/>
-      <c r="Q275" t="n">
+      <c r="Q275" t="inlineStr"/>
+      <c r="R275" t="inlineStr"/>
+      <c r="S275" t="n">
+        <v>2</v>
+      </c>
+      <c r="T275" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12355,12 +14292,19 @@
       <c r="K276" t="n">
         <v>0</v>
       </c>
-      <c r="L276" t="inlineStr"/>
+      <c r="L276" t="n">
+        <v>0</v>
+      </c>
       <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr"/>
-      <c r="Q276" t="n">
+      <c r="Q276" t="inlineStr"/>
+      <c r="R276" t="inlineStr"/>
+      <c r="S276" t="n">
+        <v>1</v>
+      </c>
+      <c r="T276" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12398,12 +14342,19 @@
       <c r="K277" t="n">
         <v>0</v>
       </c>
-      <c r="L277" t="inlineStr"/>
+      <c r="L277" t="n">
+        <v>0</v>
+      </c>
       <c r="M277" t="inlineStr"/>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr"/>
-      <c r="Q277" t="n">
+      <c r="Q277" t="inlineStr"/>
+      <c r="R277" t="inlineStr"/>
+      <c r="S277" t="n">
+        <v>1</v>
+      </c>
+      <c r="T277" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12441,12 +14392,19 @@
       <c r="K278" t="n">
         <v>1</v>
       </c>
-      <c r="L278" t="inlineStr"/>
+      <c r="L278" t="n">
+        <v>0</v>
+      </c>
       <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
       <c r="P278" t="inlineStr"/>
-      <c r="Q278" t="n">
+      <c r="Q278" t="inlineStr"/>
+      <c r="R278" t="inlineStr"/>
+      <c r="S278" t="n">
+        <v>3</v>
+      </c>
+      <c r="T278" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12484,12 +14442,19 @@
       <c r="K279" t="n">
         <v>0</v>
       </c>
-      <c r="L279" t="inlineStr"/>
+      <c r="L279" t="n">
+        <v>0</v>
+      </c>
       <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr"/>
-      <c r="Q279" t="n">
+      <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
+      <c r="S279" t="n">
+        <v>3</v>
+      </c>
+      <c r="T279" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12527,12 +14492,19 @@
       <c r="K280" t="n">
         <v>0</v>
       </c>
-      <c r="L280" t="inlineStr"/>
+      <c r="L280" t="n">
+        <v>0</v>
+      </c>
       <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
       <c r="P280" t="inlineStr"/>
-      <c r="Q280" t="n">
+      <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
+      <c r="S280" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12570,12 +14542,19 @@
       <c r="K281" t="n">
         <v>0</v>
       </c>
-      <c r="L281" t="inlineStr"/>
+      <c r="L281" t="n">
+        <v>0</v>
+      </c>
       <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr"/>
       <c r="P281" t="inlineStr"/>
-      <c r="Q281" t="n">
+      <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
+      <c r="S281" t="n">
+        <v>7</v>
+      </c>
+      <c r="T281" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12613,12 +14592,19 @@
       <c r="K282" t="n">
         <v>3</v>
       </c>
-      <c r="L282" t="inlineStr"/>
+      <c r="L282" t="n">
+        <v>0</v>
+      </c>
       <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr"/>
       <c r="P282" t="inlineStr"/>
-      <c r="Q282" t="n">
+      <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
+      <c r="S282" t="n">
+        <v>7</v>
+      </c>
+      <c r="T282" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12656,12 +14642,19 @@
       <c r="K283" t="n">
         <v>0</v>
       </c>
-      <c r="L283" t="inlineStr"/>
+      <c r="L283" t="n">
+        <v>0</v>
+      </c>
       <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr"/>
       <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="n">
+      <c r="Q283" t="inlineStr"/>
+      <c r="R283" t="inlineStr"/>
+      <c r="S283" t="n">
+        <v>1</v>
+      </c>
+      <c r="T283" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12699,12 +14692,19 @@
       <c r="K284" t="n">
         <v>1</v>
       </c>
-      <c r="L284" t="inlineStr"/>
+      <c r="L284" t="n">
+        <v>0</v>
+      </c>
       <c r="M284" t="inlineStr"/>
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="inlineStr"/>
       <c r="P284" t="inlineStr"/>
-      <c r="Q284" t="n">
+      <c r="Q284" t="inlineStr"/>
+      <c r="R284" t="inlineStr"/>
+      <c r="S284" t="n">
+        <v>2</v>
+      </c>
+      <c r="T284" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12742,12 +14742,19 @@
       <c r="K285" t="n">
         <v>2</v>
       </c>
-      <c r="L285" t="inlineStr"/>
+      <c r="L285" t="n">
+        <v>0</v>
+      </c>
       <c r="M285" t="inlineStr"/>
       <c r="N285" t="inlineStr"/>
       <c r="O285" t="inlineStr"/>
       <c r="P285" t="inlineStr"/>
-      <c r="Q285" t="n">
+      <c r="Q285" t="inlineStr"/>
+      <c r="R285" t="inlineStr"/>
+      <c r="S285" t="n">
+        <v>2</v>
+      </c>
+      <c r="T285" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12785,12 +14792,19 @@
       <c r="K286" t="n">
         <v>0</v>
       </c>
-      <c r="L286" t="inlineStr"/>
+      <c r="L286" t="n">
+        <v>1</v>
+      </c>
       <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr"/>
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="inlineStr"/>
-      <c r="Q286" t="n">
+      <c r="Q286" t="inlineStr"/>
+      <c r="R286" t="inlineStr"/>
+      <c r="S286" t="n">
+        <v>4</v>
+      </c>
+      <c r="T286" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12828,12 +14842,19 @@
       <c r="K287" t="n">
         <v>3</v>
       </c>
-      <c r="L287" t="inlineStr"/>
+      <c r="L287" t="n">
+        <v>0</v>
+      </c>
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr"/>
-      <c r="Q287" t="n">
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
+      <c r="S287" t="n">
+        <v>5</v>
+      </c>
+      <c r="T287" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12871,12 +14892,19 @@
       <c r="K288" t="n">
         <v>0</v>
       </c>
-      <c r="L288" t="inlineStr"/>
+      <c r="L288" t="n">
+        <v>0</v>
+      </c>
       <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr"/>
-      <c r="Q288" t="n">
+      <c r="Q288" t="inlineStr"/>
+      <c r="R288" t="inlineStr"/>
+      <c r="S288" t="n">
+        <v>8</v>
+      </c>
+      <c r="T288" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12914,12 +14942,19 @@
       <c r="K289" t="n">
         <v>0</v>
       </c>
-      <c r="L289" t="inlineStr"/>
+      <c r="L289" t="n">
+        <v>0</v>
+      </c>
       <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
       <c r="P289" t="inlineStr"/>
-      <c r="Q289" t="n">
+      <c r="Q289" t="inlineStr"/>
+      <c r="R289" t="inlineStr"/>
+      <c r="S289" t="n">
+        <v>14</v>
+      </c>
+      <c r="T289" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -12957,12 +14992,19 @@
       <c r="K290" t="n">
         <v>0</v>
       </c>
-      <c r="L290" t="inlineStr"/>
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
       <c r="M290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
       <c r="O290" t="inlineStr"/>
       <c r="P290" t="inlineStr"/>
-      <c r="Q290" t="n">
+      <c r="Q290" t="inlineStr"/>
+      <c r="R290" t="inlineStr"/>
+      <c r="S290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T290" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13000,12 +15042,19 @@
       <c r="K291" t="n">
         <v>0</v>
       </c>
-      <c r="L291" t="inlineStr"/>
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
       <c r="M291" t="inlineStr"/>
       <c r="N291" t="inlineStr"/>
       <c r="O291" t="inlineStr"/>
       <c r="P291" t="inlineStr"/>
-      <c r="Q291" t="n">
+      <c r="Q291" t="inlineStr"/>
+      <c r="R291" t="inlineStr"/>
+      <c r="S291" t="n">
+        <v>2</v>
+      </c>
+      <c r="T291" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13043,12 +15092,19 @@
       <c r="K292" t="n">
         <v>1</v>
       </c>
-      <c r="L292" t="inlineStr"/>
+      <c r="L292" t="n">
+        <v>0</v>
+      </c>
       <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr"/>
       <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr"/>
-      <c r="Q292" t="n">
+      <c r="Q292" t="inlineStr"/>
+      <c r="R292" t="inlineStr"/>
+      <c r="S292" t="n">
+        <v>6</v>
+      </c>
+      <c r="T292" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13086,12 +15142,19 @@
       <c r="K293" t="n">
         <v>1</v>
       </c>
-      <c r="L293" t="inlineStr"/>
+      <c r="L293" t="n">
+        <v>0</v>
+      </c>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
       <c r="O293" t="inlineStr"/>
       <c r="P293" t="inlineStr"/>
-      <c r="Q293" t="n">
+      <c r="Q293" t="inlineStr"/>
+      <c r="R293" t="inlineStr"/>
+      <c r="S293" t="n">
+        <v>8</v>
+      </c>
+      <c r="T293" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13129,12 +15192,19 @@
       <c r="K294" t="n">
         <v>0</v>
       </c>
-      <c r="L294" t="inlineStr"/>
+      <c r="L294" t="n">
+        <v>0</v>
+      </c>
       <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr"/>
-      <c r="Q294" t="n">
+      <c r="Q294" t="inlineStr"/>
+      <c r="R294" t="inlineStr"/>
+      <c r="S294" t="n">
+        <v>0</v>
+      </c>
+      <c r="T294" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13172,12 +15242,19 @@
       <c r="K295" t="n">
         <v>0</v>
       </c>
-      <c r="L295" t="inlineStr"/>
+      <c r="L295" t="n">
+        <v>0</v>
+      </c>
       <c r="M295" t="inlineStr"/>
       <c r="N295" t="inlineStr"/>
       <c r="O295" t="inlineStr"/>
       <c r="P295" t="inlineStr"/>
-      <c r="Q295" t="n">
+      <c r="Q295" t="inlineStr"/>
+      <c r="R295" t="inlineStr"/>
+      <c r="S295" t="n">
+        <v>2</v>
+      </c>
+      <c r="T295" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13215,12 +15292,19 @@
       <c r="K296" t="n">
         <v>0</v>
       </c>
-      <c r="L296" t="inlineStr"/>
+      <c r="L296" t="n">
+        <v>0</v>
+      </c>
       <c r="M296" t="inlineStr"/>
       <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr"/>
-      <c r="Q296" t="n">
+      <c r="Q296" t="inlineStr"/>
+      <c r="R296" t="inlineStr"/>
+      <c r="S296" t="n">
+        <v>1</v>
+      </c>
+      <c r="T296" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13258,12 +15342,19 @@
       <c r="K297" t="n">
         <v>0</v>
       </c>
-      <c r="L297" t="inlineStr"/>
+      <c r="L297" t="n">
+        <v>0</v>
+      </c>
       <c r="M297" t="inlineStr"/>
       <c r="N297" t="inlineStr"/>
       <c r="O297" t="inlineStr"/>
       <c r="P297" t="inlineStr"/>
-      <c r="Q297" t="n">
+      <c r="Q297" t="inlineStr"/>
+      <c r="R297" t="inlineStr"/>
+      <c r="S297" t="n">
+        <v>4</v>
+      </c>
+      <c r="T297" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13301,12 +15392,19 @@
       <c r="K298" t="n">
         <v>0</v>
       </c>
-      <c r="L298" t="inlineStr"/>
+      <c r="L298" t="n">
+        <v>0</v>
+      </c>
       <c r="M298" t="inlineStr"/>
       <c r="N298" t="inlineStr"/>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="inlineStr"/>
-      <c r="Q298" t="n">
+      <c r="Q298" t="inlineStr"/>
+      <c r="R298" t="inlineStr"/>
+      <c r="S298" t="n">
+        <v>0</v>
+      </c>
+      <c r="T298" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13344,12 +15442,19 @@
       <c r="K299" t="n">
         <v>0</v>
       </c>
-      <c r="L299" t="inlineStr"/>
+      <c r="L299" t="n">
+        <v>0</v>
+      </c>
       <c r="M299" t="inlineStr"/>
       <c r="N299" t="inlineStr"/>
       <c r="O299" t="inlineStr"/>
       <c r="P299" t="inlineStr"/>
-      <c r="Q299" t="n">
+      <c r="Q299" t="inlineStr"/>
+      <c r="R299" t="inlineStr"/>
+      <c r="S299" t="n">
+        <v>1</v>
+      </c>
+      <c r="T299" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13379,12 +15484,10 @@
       <c r="K300" t="n">
         <v>0</v>
       </c>
-      <c r="L300" t="n">
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="n">
         <v>6</v>
       </c>
-      <c r="M300" t="n">
-        <v>0</v>
-      </c>
       <c r="N300" t="n">
         <v>0</v>
       </c>
@@ -13392,9 +15495,18 @@
         <v>0</v>
       </c>
       <c r="P300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q300" t="n">
+        <v>1</v>
+      </c>
+      <c r="R300" t="n">
+        <v>0</v>
+      </c>
+      <c r="S300" t="n">
+        <v>0</v>
+      </c>
+      <c r="T300" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13432,12 +15544,19 @@
       <c r="K301" t="n">
         <v>0</v>
       </c>
-      <c r="L301" t="inlineStr"/>
+      <c r="L301" t="n">
+        <v>0</v>
+      </c>
       <c r="M301" t="inlineStr"/>
       <c r="N301" t="inlineStr"/>
       <c r="O301" t="inlineStr"/>
       <c r="P301" t="inlineStr"/>
-      <c r="Q301" t="n">
+      <c r="Q301" t="inlineStr"/>
+      <c r="R301" t="inlineStr"/>
+      <c r="S301" t="n">
+        <v>1</v>
+      </c>
+      <c r="T301" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13475,12 +15594,19 @@
       <c r="K302" t="n">
         <v>0</v>
       </c>
-      <c r="L302" t="inlineStr"/>
+      <c r="L302" t="n">
+        <v>0</v>
+      </c>
       <c r="M302" t="inlineStr"/>
       <c r="N302" t="inlineStr"/>
       <c r="O302" t="inlineStr"/>
       <c r="P302" t="inlineStr"/>
-      <c r="Q302" t="n">
+      <c r="Q302" t="inlineStr"/>
+      <c r="R302" t="inlineStr"/>
+      <c r="S302" t="n">
+        <v>3</v>
+      </c>
+      <c r="T302" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13518,12 +15644,19 @@
       <c r="K303" t="n">
         <v>1</v>
       </c>
-      <c r="L303" t="inlineStr"/>
+      <c r="L303" t="n">
+        <v>0</v>
+      </c>
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr"/>
       <c r="O303" t="inlineStr"/>
       <c r="P303" t="inlineStr"/>
-      <c r="Q303" t="n">
+      <c r="Q303" t="inlineStr"/>
+      <c r="R303" t="inlineStr"/>
+      <c r="S303" t="n">
+        <v>5</v>
+      </c>
+      <c r="T303" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13561,12 +15694,19 @@
       <c r="K304" t="n">
         <v>0</v>
       </c>
-      <c r="L304" t="inlineStr"/>
+      <c r="L304" t="n">
+        <v>0</v>
+      </c>
       <c r="M304" t="inlineStr"/>
       <c r="N304" t="inlineStr"/>
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="inlineStr"/>
-      <c r="Q304" t="n">
+      <c r="Q304" t="inlineStr"/>
+      <c r="R304" t="inlineStr"/>
+      <c r="S304" t="n">
+        <v>8</v>
+      </c>
+      <c r="T304" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13604,12 +15744,19 @@
       <c r="K305" t="n">
         <v>0</v>
       </c>
-      <c r="L305" t="inlineStr"/>
+      <c r="L305" t="n">
+        <v>0</v>
+      </c>
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr"/>
       <c r="O305" t="inlineStr"/>
       <c r="P305" t="inlineStr"/>
-      <c r="Q305" t="n">
+      <c r="Q305" t="inlineStr"/>
+      <c r="R305" t="inlineStr"/>
+      <c r="S305" t="n">
+        <v>0</v>
+      </c>
+      <c r="T305" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13647,12 +15794,19 @@
       <c r="K306" t="n">
         <v>0</v>
       </c>
-      <c r="L306" t="inlineStr"/>
+      <c r="L306" t="n">
+        <v>0</v>
+      </c>
       <c r="M306" t="inlineStr"/>
       <c r="N306" t="inlineStr"/>
       <c r="O306" t="inlineStr"/>
       <c r="P306" t="inlineStr"/>
-      <c r="Q306" t="n">
+      <c r="Q306" t="inlineStr"/>
+      <c r="R306" t="inlineStr"/>
+      <c r="S306" t="n">
+        <v>0</v>
+      </c>
+      <c r="T306" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13690,12 +15844,19 @@
       <c r="K307" t="n">
         <v>0</v>
       </c>
-      <c r="L307" t="inlineStr"/>
+      <c r="L307" t="n">
+        <v>0</v>
+      </c>
       <c r="M307" t="inlineStr"/>
       <c r="N307" t="inlineStr"/>
       <c r="O307" t="inlineStr"/>
       <c r="P307" t="inlineStr"/>
-      <c r="Q307" t="n">
+      <c r="Q307" t="inlineStr"/>
+      <c r="R307" t="inlineStr"/>
+      <c r="S307" t="n">
+        <v>1</v>
+      </c>
+      <c r="T307" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13733,12 +15894,19 @@
       <c r="K308" t="n">
         <v>0</v>
       </c>
-      <c r="L308" t="inlineStr"/>
+      <c r="L308" t="n">
+        <v>0</v>
+      </c>
       <c r="M308" t="inlineStr"/>
       <c r="N308" t="inlineStr"/>
       <c r="O308" t="inlineStr"/>
       <c r="P308" t="inlineStr"/>
-      <c r="Q308" t="n">
+      <c r="Q308" t="inlineStr"/>
+      <c r="R308" t="inlineStr"/>
+      <c r="S308" t="n">
+        <v>1</v>
+      </c>
+      <c r="T308" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13776,12 +15944,19 @@
       <c r="K309" t="n">
         <v>0</v>
       </c>
-      <c r="L309" t="inlineStr"/>
+      <c r="L309" t="n">
+        <v>0</v>
+      </c>
       <c r="M309" t="inlineStr"/>
       <c r="N309" t="inlineStr"/>
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="inlineStr"/>
-      <c r="Q309" t="n">
+      <c r="Q309" t="inlineStr"/>
+      <c r="R309" t="inlineStr"/>
+      <c r="S309" t="n">
+        <v>0</v>
+      </c>
+      <c r="T309" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13819,12 +15994,19 @@
       <c r="K310" t="n">
         <v>0</v>
       </c>
-      <c r="L310" t="inlineStr"/>
+      <c r="L310" t="n">
+        <v>0</v>
+      </c>
       <c r="M310" t="inlineStr"/>
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr"/>
-      <c r="Q310" t="n">
+      <c r="Q310" t="inlineStr"/>
+      <c r="R310" t="inlineStr"/>
+      <c r="S310" t="n">
+        <v>0</v>
+      </c>
+      <c r="T310" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13862,12 +16044,19 @@
       <c r="K311" t="n">
         <v>0</v>
       </c>
-      <c r="L311" t="inlineStr"/>
+      <c r="L311" t="n">
+        <v>0</v>
+      </c>
       <c r="M311" t="inlineStr"/>
       <c r="N311" t="inlineStr"/>
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="inlineStr"/>
-      <c r="Q311" t="n">
+      <c r="Q311" t="inlineStr"/>
+      <c r="R311" t="inlineStr"/>
+      <c r="S311" t="n">
+        <v>11</v>
+      </c>
+      <c r="T311" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13905,12 +16094,19 @@
       <c r="K312" t="n">
         <v>0</v>
       </c>
-      <c r="L312" t="inlineStr"/>
+      <c r="L312" t="n">
+        <v>0</v>
+      </c>
       <c r="M312" t="inlineStr"/>
       <c r="N312" t="inlineStr"/>
       <c r="O312" t="inlineStr"/>
       <c r="P312" t="inlineStr"/>
-      <c r="Q312" t="n">
+      <c r="Q312" t="inlineStr"/>
+      <c r="R312" t="inlineStr"/>
+      <c r="S312" t="n">
+        <v>8</v>
+      </c>
+      <c r="T312" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13948,12 +16144,19 @@
       <c r="K313" t="n">
         <v>0</v>
       </c>
-      <c r="L313" t="inlineStr"/>
+      <c r="L313" t="n">
+        <v>0</v>
+      </c>
       <c r="M313" t="inlineStr"/>
       <c r="N313" t="inlineStr"/>
       <c r="O313" t="inlineStr"/>
       <c r="P313" t="inlineStr"/>
-      <c r="Q313" t="n">
+      <c r="Q313" t="inlineStr"/>
+      <c r="R313" t="inlineStr"/>
+      <c r="S313" t="n">
+        <v>0</v>
+      </c>
+      <c r="T313" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -13991,12 +16194,19 @@
       <c r="K314" t="n">
         <v>0</v>
       </c>
-      <c r="L314" t="inlineStr"/>
+      <c r="L314" t="n">
+        <v>0</v>
+      </c>
       <c r="M314" t="inlineStr"/>
       <c r="N314" t="inlineStr"/>
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="inlineStr"/>
-      <c r="Q314" t="n">
+      <c r="Q314" t="inlineStr"/>
+      <c r="R314" t="inlineStr"/>
+      <c r="S314" t="n">
+        <v>8</v>
+      </c>
+      <c r="T314" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14034,12 +16244,19 @@
       <c r="K315" t="n">
         <v>0</v>
       </c>
-      <c r="L315" t="inlineStr"/>
+      <c r="L315" t="n">
+        <v>0</v>
+      </c>
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr"/>
-      <c r="Q315" t="n">
+      <c r="Q315" t="inlineStr"/>
+      <c r="R315" t="inlineStr"/>
+      <c r="S315" t="n">
+        <v>3</v>
+      </c>
+      <c r="T315" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14077,12 +16294,19 @@
       <c r="K316" t="n">
         <v>1</v>
       </c>
-      <c r="L316" t="inlineStr"/>
+      <c r="L316" t="n">
+        <v>0</v>
+      </c>
       <c r="M316" t="inlineStr"/>
       <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="inlineStr"/>
-      <c r="Q316" t="n">
+      <c r="Q316" t="inlineStr"/>
+      <c r="R316" t="inlineStr"/>
+      <c r="S316" t="n">
+        <v>7</v>
+      </c>
+      <c r="T316" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14120,12 +16344,19 @@
       <c r="K317" t="n">
         <v>0</v>
       </c>
-      <c r="L317" t="inlineStr"/>
+      <c r="L317" t="n">
+        <v>0</v>
+      </c>
       <c r="M317" t="inlineStr"/>
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr"/>
       <c r="P317" t="inlineStr"/>
-      <c r="Q317" t="n">
+      <c r="Q317" t="inlineStr"/>
+      <c r="R317" t="inlineStr"/>
+      <c r="S317" t="n">
+        <v>7</v>
+      </c>
+      <c r="T317" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14163,12 +16394,19 @@
       <c r="K318" t="n">
         <v>0</v>
       </c>
-      <c r="L318" t="inlineStr"/>
+      <c r="L318" t="n">
+        <v>0</v>
+      </c>
       <c r="M318" t="inlineStr"/>
       <c r="N318" t="inlineStr"/>
       <c r="O318" t="inlineStr"/>
       <c r="P318" t="inlineStr"/>
-      <c r="Q318" t="n">
+      <c r="Q318" t="inlineStr"/>
+      <c r="R318" t="inlineStr"/>
+      <c r="S318" t="n">
+        <v>0</v>
+      </c>
+      <c r="T318" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14206,12 +16444,19 @@
       <c r="K319" t="n">
         <v>0</v>
       </c>
-      <c r="L319" t="inlineStr"/>
+      <c r="L319" t="n">
+        <v>0</v>
+      </c>
       <c r="M319" t="inlineStr"/>
       <c r="N319" t="inlineStr"/>
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="inlineStr"/>
-      <c r="Q319" t="n">
+      <c r="Q319" t="inlineStr"/>
+      <c r="R319" t="inlineStr"/>
+      <c r="S319" t="n">
+        <v>0</v>
+      </c>
+      <c r="T319" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14249,12 +16494,19 @@
       <c r="K320" t="n">
         <v>0</v>
       </c>
-      <c r="L320" t="inlineStr"/>
+      <c r="L320" t="n">
+        <v>0</v>
+      </c>
       <c r="M320" t="inlineStr"/>
       <c r="N320" t="inlineStr"/>
       <c r="O320" t="inlineStr"/>
       <c r="P320" t="inlineStr"/>
-      <c r="Q320" t="n">
+      <c r="Q320" t="inlineStr"/>
+      <c r="R320" t="inlineStr"/>
+      <c r="S320" t="n">
+        <v>1</v>
+      </c>
+      <c r="T320" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14292,12 +16544,19 @@
       <c r="K321" t="n">
         <v>0</v>
       </c>
-      <c r="L321" t="inlineStr"/>
+      <c r="L321" t="n">
+        <v>0</v>
+      </c>
       <c r="M321" t="inlineStr"/>
       <c r="N321" t="inlineStr"/>
       <c r="O321" t="inlineStr"/>
       <c r="P321" t="inlineStr"/>
-      <c r="Q321" t="n">
+      <c r="Q321" t="inlineStr"/>
+      <c r="R321" t="inlineStr"/>
+      <c r="S321" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14335,12 +16594,19 @@
       <c r="K322" t="n">
         <v>0</v>
       </c>
-      <c r="L322" t="inlineStr"/>
+      <c r="L322" t="n">
+        <v>0</v>
+      </c>
       <c r="M322" t="inlineStr"/>
       <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="inlineStr"/>
-      <c r="Q322" t="n">
+      <c r="Q322" t="inlineStr"/>
+      <c r="R322" t="inlineStr"/>
+      <c r="S322" t="n">
+        <v>4</v>
+      </c>
+      <c r="T322" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14378,12 +16644,19 @@
       <c r="K323" t="n">
         <v>0</v>
       </c>
-      <c r="L323" t="inlineStr"/>
+      <c r="L323" t="n">
+        <v>0</v>
+      </c>
       <c r="M323" t="inlineStr"/>
       <c r="N323" t="inlineStr"/>
       <c r="O323" t="inlineStr"/>
       <c r="P323" t="inlineStr"/>
-      <c r="Q323" t="n">
+      <c r="Q323" t="inlineStr"/>
+      <c r="R323" t="inlineStr"/>
+      <c r="S323" t="n">
+        <v>0</v>
+      </c>
+      <c r="T323" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14421,12 +16694,19 @@
       <c r="K324" t="n">
         <v>0</v>
       </c>
-      <c r="L324" t="inlineStr"/>
+      <c r="L324" t="n">
+        <v>0</v>
+      </c>
       <c r="M324" t="inlineStr"/>
       <c r="N324" t="inlineStr"/>
       <c r="O324" t="inlineStr"/>
       <c r="P324" t="inlineStr"/>
-      <c r="Q324" t="n">
+      <c r="Q324" t="inlineStr"/>
+      <c r="R324" t="inlineStr"/>
+      <c r="S324" t="n">
+        <v>13</v>
+      </c>
+      <c r="T324" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14464,12 +16744,19 @@
       <c r="K325" t="n">
         <v>0</v>
       </c>
-      <c r="L325" t="inlineStr"/>
+      <c r="L325" t="n">
+        <v>0</v>
+      </c>
       <c r="M325" t="inlineStr"/>
       <c r="N325" t="inlineStr"/>
       <c r="O325" t="inlineStr"/>
       <c r="P325" t="inlineStr"/>
-      <c r="Q325" t="n">
+      <c r="Q325" t="inlineStr"/>
+      <c r="R325" t="inlineStr"/>
+      <c r="S325" t="n">
+        <v>3</v>
+      </c>
+      <c r="T325" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14507,12 +16794,19 @@
       <c r="K326" t="n">
         <v>0</v>
       </c>
-      <c r="L326" t="inlineStr"/>
+      <c r="L326" t="n">
+        <v>0</v>
+      </c>
       <c r="M326" t="inlineStr"/>
       <c r="N326" t="inlineStr"/>
       <c r="O326" t="inlineStr"/>
       <c r="P326" t="inlineStr"/>
-      <c r="Q326" t="n">
+      <c r="Q326" t="inlineStr"/>
+      <c r="R326" t="inlineStr"/>
+      <c r="S326" t="n">
+        <v>1</v>
+      </c>
+      <c r="T326" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14550,12 +16844,19 @@
       <c r="K327" t="n">
         <v>0</v>
       </c>
-      <c r="L327" t="inlineStr"/>
+      <c r="L327" t="n">
+        <v>0</v>
+      </c>
       <c r="M327" t="inlineStr"/>
       <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr"/>
       <c r="P327" t="inlineStr"/>
-      <c r="Q327" t="n">
+      <c r="Q327" t="inlineStr"/>
+      <c r="R327" t="inlineStr"/>
+      <c r="S327" t="n">
+        <v>4</v>
+      </c>
+      <c r="T327" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14593,12 +16894,19 @@
       <c r="K328" t="n">
         <v>0</v>
       </c>
-      <c r="L328" t="inlineStr"/>
+      <c r="L328" t="n">
+        <v>0</v>
+      </c>
       <c r="M328" t="inlineStr"/>
       <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="inlineStr"/>
-      <c r="Q328" t="n">
+      <c r="Q328" t="inlineStr"/>
+      <c r="R328" t="inlineStr"/>
+      <c r="S328" t="n">
+        <v>0</v>
+      </c>
+      <c r="T328" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14636,12 +16944,19 @@
       <c r="K329" t="n">
         <v>0</v>
       </c>
-      <c r="L329" t="inlineStr"/>
+      <c r="L329" t="n">
+        <v>0</v>
+      </c>
       <c r="M329" t="inlineStr"/>
       <c r="N329" t="inlineStr"/>
       <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr"/>
-      <c r="Q329" t="n">
+      <c r="Q329" t="inlineStr"/>
+      <c r="R329" t="inlineStr"/>
+      <c r="S329" t="n">
+        <v>1</v>
+      </c>
+      <c r="T329" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14679,12 +16994,19 @@
       <c r="K330" t="n">
         <v>0</v>
       </c>
-      <c r="L330" t="inlineStr"/>
+      <c r="L330" t="n">
+        <v>0</v>
+      </c>
       <c r="M330" t="inlineStr"/>
       <c r="N330" t="inlineStr"/>
       <c r="O330" t="inlineStr"/>
       <c r="P330" t="inlineStr"/>
-      <c r="Q330" t="n">
+      <c r="Q330" t="inlineStr"/>
+      <c r="R330" t="inlineStr"/>
+      <c r="S330" t="n">
+        <v>3</v>
+      </c>
+      <c r="T330" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14722,12 +17044,19 @@
       <c r="K331" t="n">
         <v>0</v>
       </c>
-      <c r="L331" t="inlineStr"/>
+      <c r="L331" t="n">
+        <v>0</v>
+      </c>
       <c r="M331" t="inlineStr"/>
       <c r="N331" t="inlineStr"/>
       <c r="O331" t="inlineStr"/>
       <c r="P331" t="inlineStr"/>
-      <c r="Q331" t="n">
+      <c r="Q331" t="inlineStr"/>
+      <c r="R331" t="inlineStr"/>
+      <c r="S331" t="n">
+        <v>2</v>
+      </c>
+      <c r="T331" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14765,12 +17094,19 @@
       <c r="K332" t="n">
         <v>0</v>
       </c>
-      <c r="L332" t="inlineStr"/>
+      <c r="L332" t="n">
+        <v>0</v>
+      </c>
       <c r="M332" t="inlineStr"/>
       <c r="N332" t="inlineStr"/>
       <c r="O332" t="inlineStr"/>
       <c r="P332" t="inlineStr"/>
-      <c r="Q332" t="n">
+      <c r="Q332" t="inlineStr"/>
+      <c r="R332" t="inlineStr"/>
+      <c r="S332" t="n">
+        <v>1</v>
+      </c>
+      <c r="T332" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14824,6 +17160,15 @@
         <v>0</v>
       </c>
       <c r="Q333" t="n">
+        <v>0</v>
+      </c>
+      <c r="R333" t="n">
+        <v>0</v>
+      </c>
+      <c r="S333" t="n">
+        <v>0</v>
+      </c>
+      <c r="T333" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14877,6 +17222,15 @@
         <v>0</v>
       </c>
       <c r="Q334" t="n">
+        <v>0</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0</v>
+      </c>
+      <c r="S334" t="n">
+        <v>2</v>
+      </c>
+      <c r="T334" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14914,12 +17268,19 @@
       <c r="K335" t="n">
         <v>1</v>
       </c>
-      <c r="L335" t="inlineStr"/>
+      <c r="L335" t="n">
+        <v>0</v>
+      </c>
       <c r="M335" t="inlineStr"/>
       <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr"/>
       <c r="P335" t="inlineStr"/>
-      <c r="Q335" t="n">
+      <c r="Q335" t="inlineStr"/>
+      <c r="R335" t="inlineStr"/>
+      <c r="S335" t="n">
+        <v>4</v>
+      </c>
+      <c r="T335" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -14957,12 +17318,19 @@
       <c r="K336" t="n">
         <v>0</v>
       </c>
-      <c r="L336" t="inlineStr"/>
+      <c r="L336" t="n">
+        <v>0</v>
+      </c>
       <c r="M336" t="inlineStr"/>
       <c r="N336" t="inlineStr"/>
       <c r="O336" t="inlineStr"/>
       <c r="P336" t="inlineStr"/>
-      <c r="Q336" t="n">
+      <c r="Q336" t="inlineStr"/>
+      <c r="R336" t="inlineStr"/>
+      <c r="S336" t="n">
+        <v>8</v>
+      </c>
+      <c r="T336" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15016,6 +17384,15 @@
         <v>0</v>
       </c>
       <c r="Q337" t="n">
+        <v>0</v>
+      </c>
+      <c r="R337" t="n">
+        <v>0</v>
+      </c>
+      <c r="S337" t="n">
+        <v>0</v>
+      </c>
+      <c r="T337" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15053,12 +17430,19 @@
       <c r="K338" t="n">
         <v>0</v>
       </c>
-      <c r="L338" t="inlineStr"/>
+      <c r="L338" t="n">
+        <v>0</v>
+      </c>
       <c r="M338" t="inlineStr"/>
       <c r="N338" t="inlineStr"/>
       <c r="O338" t="inlineStr"/>
       <c r="P338" t="inlineStr"/>
-      <c r="Q338" t="n">
+      <c r="Q338" t="inlineStr"/>
+      <c r="R338" t="inlineStr"/>
+      <c r="S338" t="n">
+        <v>6</v>
+      </c>
+      <c r="T338" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15096,12 +17480,19 @@
       <c r="K339" t="n">
         <v>0</v>
       </c>
-      <c r="L339" t="inlineStr"/>
+      <c r="L339" t="n">
+        <v>0</v>
+      </c>
       <c r="M339" t="inlineStr"/>
       <c r="N339" t="inlineStr"/>
       <c r="O339" t="inlineStr"/>
       <c r="P339" t="inlineStr"/>
-      <c r="Q339" t="n">
+      <c r="Q339" t="inlineStr"/>
+      <c r="R339" t="inlineStr"/>
+      <c r="S339" t="n">
+        <v>3</v>
+      </c>
+      <c r="T339" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15139,12 +17530,19 @@
       <c r="K340" t="n">
         <v>0</v>
       </c>
-      <c r="L340" t="inlineStr"/>
+      <c r="L340" t="n">
+        <v>0</v>
+      </c>
       <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr"/>
       <c r="O340" t="inlineStr"/>
       <c r="P340" t="inlineStr"/>
-      <c r="Q340" t="n">
+      <c r="Q340" t="inlineStr"/>
+      <c r="R340" t="inlineStr"/>
+      <c r="S340" t="n">
+        <v>0</v>
+      </c>
+      <c r="T340" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15182,12 +17580,19 @@
       <c r="K341" t="n">
         <v>0</v>
       </c>
-      <c r="L341" t="inlineStr"/>
+      <c r="L341" t="n">
+        <v>0</v>
+      </c>
       <c r="M341" t="inlineStr"/>
       <c r="N341" t="inlineStr"/>
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="inlineStr"/>
-      <c r="Q341" t="n">
+      <c r="Q341" t="inlineStr"/>
+      <c r="R341" t="inlineStr"/>
+      <c r="S341" t="n">
+        <v>0</v>
+      </c>
+      <c r="T341" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15225,12 +17630,19 @@
       <c r="K342" t="n">
         <v>0</v>
       </c>
-      <c r="L342" t="inlineStr"/>
+      <c r="L342" t="n">
+        <v>0</v>
+      </c>
       <c r="M342" t="inlineStr"/>
       <c r="N342" t="inlineStr"/>
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr"/>
-      <c r="Q342" t="n">
+      <c r="Q342" t="inlineStr"/>
+      <c r="R342" t="inlineStr"/>
+      <c r="S342" t="n">
+        <v>6</v>
+      </c>
+      <c r="T342" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15268,12 +17680,19 @@
       <c r="K343" t="n">
         <v>0</v>
       </c>
-      <c r="L343" t="inlineStr"/>
+      <c r="L343" t="n">
+        <v>0</v>
+      </c>
       <c r="M343" t="inlineStr"/>
       <c r="N343" t="inlineStr"/>
       <c r="O343" t="inlineStr"/>
       <c r="P343" t="inlineStr"/>
-      <c r="Q343" t="n">
+      <c r="Q343" t="inlineStr"/>
+      <c r="R343" t="inlineStr"/>
+      <c r="S343" t="n">
+        <v>1</v>
+      </c>
+      <c r="T343" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15311,12 +17730,19 @@
       <c r="K344" t="n">
         <v>0</v>
       </c>
-      <c r="L344" t="inlineStr"/>
+      <c r="L344" t="n">
+        <v>0</v>
+      </c>
       <c r="M344" t="inlineStr"/>
       <c r="N344" t="inlineStr"/>
       <c r="O344" t="inlineStr"/>
       <c r="P344" t="inlineStr"/>
-      <c r="Q344" t="n">
+      <c r="Q344" t="inlineStr"/>
+      <c r="R344" t="inlineStr"/>
+      <c r="S344" t="n">
+        <v>1</v>
+      </c>
+      <c r="T344" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15370,6 +17796,15 @@
         <v>0</v>
       </c>
       <c r="Q345" t="n">
+        <v>0</v>
+      </c>
+      <c r="R345" t="n">
+        <v>0</v>
+      </c>
+      <c r="S345" t="n">
+        <v>4</v>
+      </c>
+      <c r="T345" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15423,6 +17858,15 @@
         <v>0</v>
       </c>
       <c r="Q346" t="n">
+        <v>0</v>
+      </c>
+      <c r="R346" t="n">
+        <v>0</v>
+      </c>
+      <c r="S346" t="n">
+        <v>6</v>
+      </c>
+      <c r="T346" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15460,12 +17904,19 @@
       <c r="K347" t="n">
         <v>0</v>
       </c>
-      <c r="L347" t="inlineStr"/>
+      <c r="L347" t="n">
+        <v>0</v>
+      </c>
       <c r="M347" t="inlineStr"/>
       <c r="N347" t="inlineStr"/>
       <c r="O347" t="inlineStr"/>
       <c r="P347" t="inlineStr"/>
-      <c r="Q347" t="n">
+      <c r="Q347" t="inlineStr"/>
+      <c r="R347" t="inlineStr"/>
+      <c r="S347" t="n">
+        <v>0</v>
+      </c>
+      <c r="T347" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15503,12 +17954,19 @@
       <c r="K348" t="n">
         <v>1</v>
       </c>
-      <c r="L348" t="inlineStr"/>
+      <c r="L348" t="n">
+        <v>0</v>
+      </c>
       <c r="M348" t="inlineStr"/>
       <c r="N348" t="inlineStr"/>
       <c r="O348" t="inlineStr"/>
       <c r="P348" t="inlineStr"/>
-      <c r="Q348" t="n">
+      <c r="Q348" t="inlineStr"/>
+      <c r="R348" t="inlineStr"/>
+      <c r="S348" t="n">
+        <v>2</v>
+      </c>
+      <c r="T348" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15546,12 +18004,19 @@
       <c r="K349" t="n">
         <v>3</v>
       </c>
-      <c r="L349" t="inlineStr"/>
+      <c r="L349" t="n">
+        <v>0</v>
+      </c>
       <c r="M349" t="inlineStr"/>
       <c r="N349" t="inlineStr"/>
       <c r="O349" t="inlineStr"/>
       <c r="P349" t="inlineStr"/>
-      <c r="Q349" t="n">
+      <c r="Q349" t="inlineStr"/>
+      <c r="R349" t="inlineStr"/>
+      <c r="S349" t="n">
+        <v>2</v>
+      </c>
+      <c r="T349" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15589,12 +18054,19 @@
       <c r="K350" t="n">
         <v>2</v>
       </c>
-      <c r="L350" t="inlineStr"/>
+      <c r="L350" t="n">
+        <v>0</v>
+      </c>
       <c r="M350" t="inlineStr"/>
       <c r="N350" t="inlineStr"/>
       <c r="O350" t="inlineStr"/>
       <c r="P350" t="inlineStr"/>
-      <c r="Q350" t="n">
+      <c r="Q350" t="inlineStr"/>
+      <c r="R350" t="inlineStr"/>
+      <c r="S350" t="n">
+        <v>1</v>
+      </c>
+      <c r="T350" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15632,12 +18104,19 @@
       <c r="K351" t="n">
         <v>0</v>
       </c>
-      <c r="L351" t="inlineStr"/>
+      <c r="L351" t="n">
+        <v>0</v>
+      </c>
       <c r="M351" t="inlineStr"/>
       <c r="N351" t="inlineStr"/>
       <c r="O351" t="inlineStr"/>
       <c r="P351" t="inlineStr"/>
-      <c r="Q351" t="n">
+      <c r="Q351" t="inlineStr"/>
+      <c r="R351" t="inlineStr"/>
+      <c r="S351" t="n">
+        <v>2</v>
+      </c>
+      <c r="T351" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15675,12 +18154,19 @@
       <c r="K352" t="n">
         <v>0</v>
       </c>
-      <c r="L352" t="inlineStr"/>
+      <c r="L352" t="n">
+        <v>0</v>
+      </c>
       <c r="M352" t="inlineStr"/>
       <c r="N352" t="inlineStr"/>
       <c r="O352" t="inlineStr"/>
       <c r="P352" t="inlineStr"/>
-      <c r="Q352" t="n">
+      <c r="Q352" t="inlineStr"/>
+      <c r="R352" t="inlineStr"/>
+      <c r="S352" t="n">
+        <v>2</v>
+      </c>
+      <c r="T352" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15718,12 +18204,19 @@
       <c r="K353" t="n">
         <v>0</v>
       </c>
-      <c r="L353" t="inlineStr"/>
+      <c r="L353" t="n">
+        <v>0</v>
+      </c>
       <c r="M353" t="inlineStr"/>
       <c r="N353" t="inlineStr"/>
       <c r="O353" t="inlineStr"/>
       <c r="P353" t="inlineStr"/>
-      <c r="Q353" t="n">
+      <c r="Q353" t="inlineStr"/>
+      <c r="R353" t="inlineStr"/>
+      <c r="S353" t="n">
+        <v>3</v>
+      </c>
+      <c r="T353" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15761,12 +18254,19 @@
       <c r="K354" t="n">
         <v>0</v>
       </c>
-      <c r="L354" t="inlineStr"/>
+      <c r="L354" t="n">
+        <v>0</v>
+      </c>
       <c r="M354" t="inlineStr"/>
       <c r="N354" t="inlineStr"/>
       <c r="O354" t="inlineStr"/>
       <c r="P354" t="inlineStr"/>
-      <c r="Q354" t="n">
+      <c r="Q354" t="inlineStr"/>
+      <c r="R354" t="inlineStr"/>
+      <c r="S354" t="n">
+        <v>0</v>
+      </c>
+      <c r="T354" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15804,12 +18304,19 @@
       <c r="K355" t="n">
         <v>0</v>
       </c>
-      <c r="L355" t="inlineStr"/>
+      <c r="L355" t="n">
+        <v>0</v>
+      </c>
       <c r="M355" t="inlineStr"/>
       <c r="N355" t="inlineStr"/>
       <c r="O355" t="inlineStr"/>
       <c r="P355" t="inlineStr"/>
-      <c r="Q355" t="n">
+      <c r="Q355" t="inlineStr"/>
+      <c r="R355" t="inlineStr"/>
+      <c r="S355" t="n">
+        <v>5</v>
+      </c>
+      <c r="T355" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15847,12 +18354,19 @@
       <c r="K356" t="n">
         <v>0</v>
       </c>
-      <c r="L356" t="inlineStr"/>
+      <c r="L356" t="n">
+        <v>0</v>
+      </c>
       <c r="M356" t="inlineStr"/>
       <c r="N356" t="inlineStr"/>
       <c r="O356" t="inlineStr"/>
       <c r="P356" t="inlineStr"/>
-      <c r="Q356" t="n">
+      <c r="Q356" t="inlineStr"/>
+      <c r="R356" t="inlineStr"/>
+      <c r="S356" t="n">
+        <v>0</v>
+      </c>
+      <c r="T356" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15890,12 +18404,19 @@
       <c r="K357" t="n">
         <v>0</v>
       </c>
-      <c r="L357" t="inlineStr"/>
+      <c r="L357" t="n">
+        <v>0</v>
+      </c>
       <c r="M357" t="inlineStr"/>
       <c r="N357" t="inlineStr"/>
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="inlineStr"/>
-      <c r="Q357" t="n">
+      <c r="Q357" t="inlineStr"/>
+      <c r="R357" t="inlineStr"/>
+      <c r="S357" t="n">
+        <v>5</v>
+      </c>
+      <c r="T357" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15933,12 +18454,19 @@
       <c r="K358" t="n">
         <v>0</v>
       </c>
-      <c r="L358" t="inlineStr"/>
+      <c r="L358" t="n">
+        <v>0</v>
+      </c>
       <c r="M358" t="inlineStr"/>
       <c r="N358" t="inlineStr"/>
       <c r="O358" t="inlineStr"/>
       <c r="P358" t="inlineStr"/>
-      <c r="Q358" t="n">
+      <c r="Q358" t="inlineStr"/>
+      <c r="R358" t="inlineStr"/>
+      <c r="S358" t="n">
+        <v>0</v>
+      </c>
+      <c r="T358" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -15976,12 +18504,19 @@
       <c r="K359" t="n">
         <v>0</v>
       </c>
-      <c r="L359" t="inlineStr"/>
+      <c r="L359" t="n">
+        <v>0</v>
+      </c>
       <c r="M359" t="inlineStr"/>
       <c r="N359" t="inlineStr"/>
       <c r="O359" t="inlineStr"/>
       <c r="P359" t="inlineStr"/>
-      <c r="Q359" t="n">
+      <c r="Q359" t="inlineStr"/>
+      <c r="R359" t="inlineStr"/>
+      <c r="S359" t="n">
+        <v>3</v>
+      </c>
+      <c r="T359" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -16019,12 +18554,19 @@
       <c r="K360" t="n">
         <v>5</v>
       </c>
-      <c r="L360" t="inlineStr"/>
+      <c r="L360" t="n">
+        <v>0</v>
+      </c>
       <c r="M360" t="inlineStr"/>
       <c r="N360" t="inlineStr"/>
       <c r="O360" t="inlineStr"/>
       <c r="P360" t="inlineStr"/>
-      <c r="Q360" t="n">
+      <c r="Q360" t="inlineStr"/>
+      <c r="R360" t="inlineStr"/>
+      <c r="S360" t="n">
+        <v>12</v>
+      </c>
+      <c r="T360" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -16062,12 +18604,19 @@
       <c r="K361" t="n">
         <v>0</v>
       </c>
-      <c r="L361" t="inlineStr"/>
+      <c r="L361" t="n">
+        <v>0</v>
+      </c>
       <c r="M361" t="inlineStr"/>
       <c r="N361" t="inlineStr"/>
       <c r="O361" t="inlineStr"/>
       <c r="P361" t="inlineStr"/>
-      <c r="Q361" t="n">
+      <c r="Q361" t="inlineStr"/>
+      <c r="R361" t="inlineStr"/>
+      <c r="S361" t="n">
+        <v>7</v>
+      </c>
+      <c r="T361" t="n">
         <v>2008</v>
       </c>
     </row>
@@ -16105,12 +18654,19 @@
       <c r="K362" t="n">
         <v>0</v>
       </c>
-      <c r="L362" t="inlineStr"/>
+      <c r="L362" t="n">
+        <v>0</v>
+      </c>
       <c r="M362" t="inlineStr"/>
       <c r="N362" t="inlineStr"/>
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="inlineStr"/>
-      <c r="Q362" t="n">
+      <c r="Q362" t="inlineStr"/>
+      <c r="R362" t="inlineStr"/>
+      <c r="S362" t="n">
+        <v>17</v>
+      </c>
+      <c r="T362" t="n">
         <v>2008</v>
       </c>
     </row>
